--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,10 +62,6 @@
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -132,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -175,7 +171,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-02 ~ 2026-10-13  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, RISE</t>
+          <t>최근 5거래일 변화  ·  2026-10-02 ~ 2026-10-13  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 23억(0.4%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 7종목  /  매도 23종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 15억(0.3%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 10종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,11 +665,11 @@
         <v>301</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4852419713</v>
+        <v>4533841397</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.91%</t>
+          <t>0.00%→0.89%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -691,11 +686,11 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2485298941</v>
+        <v>-2326480183</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.42%→1.03%</t>
+          <t>1.42%→1.01%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
@@ -711,40 +706,40 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13265864480</v>
+        <v>13241070487</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>0.85%→3.40%</t>
+          <t>0.85%→3.45%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>57→211</t>
+          <t>57→230</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>에이프릴바이오</t>
+          <t>에이프릴바이오  (편출)</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-66</v>
+        <v>-112</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-941740550</v>
+        <v>-2337887380</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.12%</t>
+          <t>0.44%→0.00%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>112→46</t>
+          <t>112→0</t>
         </is>
       </c>
     </row>
@@ -758,11 +753,11 @@
         <v>67</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3788580995</v>
+        <v>3637563035</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.29%→1.01%</t>
+          <t>0.29%→1.02%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -779,11 +774,11 @@
         <v>-47</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1655856561</v>
+        <v>-1595978577</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.86%→0.50%</t>
+          <t>0.86%→0.51%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -802,11 +797,11 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>544958255</v>
+        <v>515871863</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.22%</t>
+          <t>1.06%→1.21%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
@@ -823,11 +818,11 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1460591612</v>
+        <v>-1383955633</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>3.70%→3.92%</t>
+          <t>3.70%→3.90%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -846,11 +841,11 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>997541735</v>
+        <v>965789744</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.07%</t>
+          <t>0.89%→1.09%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -860,195 +855,243 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-30</v>
+        <v>-37</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-983429739</v>
+        <v>-3227139144</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.66%</t>
+          <t>0.74%→0.09%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>137→107</t>
+          <t>42→5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>495879868</v>
+        <v>1675211556</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.11%</t>
+          <t>0.94%→1.37%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>110→120</t>
+          <t>70→92</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-325438314</v>
+        <v>-939329751</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.40%→1.46%</t>
+          <t>0.90%→0.66%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>701→673</t>
+          <t>137→107</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>958439746</v>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>1.01%→1.22%</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>110→130</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-1793399524</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>3.00%→2.43%</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>237→207</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>517880863</v>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>1.04%→1.16%</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>135→148</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-324615114</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>1.40%→1.53%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>701→673</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
           <t>브이엠</t>
         </is>
       </c>
-      <c r="B12" s="11" t="n">
+      <c r="B14" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="11" t="n">
-        <v>526063860</v>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>0.75%→0.81%</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="C14" s="11" t="n">
+        <v>486863871</v>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>0.75%→0.79%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>58→66</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>에스티팜</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>-2549175324</v>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>0.74%→0.24%</t>
-        </is>
-      </c>
-      <c r="K12" s="13" t="inlineStr">
-        <is>
-          <t>42→14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
         <is>
           <t>알지노믹스</t>
         </is>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H14" s="15" t="n">
         <v>-23</v>
       </c>
-      <c r="I13" s="15" t="n">
-        <v>-592801843</v>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>0.44%→0.28%</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="I14" s="15" t="n">
+        <v>-544340856</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>0.44%→0.27%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>81→58</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1766939531</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1.05%→1.44%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>19→25</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
         <is>
           <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
-      <c r="H14" s="15" t="n">
+      <c r="H15" s="15" t="n">
         <v>-22</v>
       </c>
-      <c r="I14" s="15" t="n">
+      <c r="I15" s="15" t="n">
         <v>-634941832</v>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>0.12%→0.00%</t>
         </is>
       </c>
-      <c r="K14" s="13" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>22→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>-21</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>-1508513600</v>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>0.48%→0.12%</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>30→9</t>
         </is>
       </c>
     </row>
@@ -1060,23 +1103,23 @@
       <c r="E16" s="17" t="n"/>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-899345761</v>
+        <v>-1422077623</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.34%</t>
+          <t>0.48%→0.12%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>171→152</t>
+          <t>30→9</t>
         </is>
       </c>
     </row>
@@ -1088,23 +1131,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-15</v>
+        <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-949619748</v>
+        <v>-818348783</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>3.00%→2.63%</t>
+          <t>1.72%→1.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>237→222</t>
+          <t>171→152</t>
         </is>
       </c>
     </row>
@@ -1116,23 +1159,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>이랜텍  (편출)</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-85612777</v>
+        <v>-719662809</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.02%→0.00%</t>
+          <t>0.58%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>71→52</t>
         </is>
       </c>
     </row>
@@ -1144,23 +1187,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>이랜텍  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-275771927</v>
+        <v>-85612777</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.44%→0.39%</t>
+          <t>0.02%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>102→90</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1172,23 +1215,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-551935854</v>
+        <v>-256367932</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>0.44%→0.38%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>102→90</t>
         </is>
       </c>
     </row>
@@ -1207,11 +1250,11 @@
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-937859751</v>
+        <v>-871023769</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.76%</t>
+          <t>1.02%→0.75%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -1228,23 +1271,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1653259561</v>
+        <v>-551935854</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.85%→1.37%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1256,23 +1299,23 @@
       <c r="E23" s="17" t="n"/>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-509011865</v>
+        <v>-858479772</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.34%</t>
+          <t>0.88%→0.64%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>48→38</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1327,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1231859673</v>
+        <v>-1588089579</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>6.77%→7.06%</t>
+          <t>1.85%→1.38%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1312,23 +1355,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-136121964</v>
+        <v>-464421877</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>0.38%→0.33%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1340,23 +1383,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-540371857</v>
+        <v>-1184819686</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.42%</t>
+          <t>6.77%→7.13%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1368,23 +1411,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-914339757</v>
+        <v>-494507869</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.56%</t>
+          <t>0.48%→0.40%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1396,731 +1439,825 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
+          <t>한텍</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-129065966</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.38%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>96→90</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
           <t>파마리서치</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-889349764</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>0.87%→0.66%</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="I29" s="15" t="n">
+        <v>-873179768</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.69%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>15→12</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 53억(1.6%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
+    <row r="30">
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-905519760</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>2.69%→2.66%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>48→45</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="17" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-475691874</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>6.18%→5.60%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>183→180</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 52억(1.6%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B32" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D32" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G35" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>앱클론</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>974988037</v>
-      </c>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>3.17%→3.51%</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>779→851</t>
-        </is>
-      </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>HLB이노베이션</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>-176</v>
-      </c>
-      <c r="I33" s="15" t="n">
-        <v>-1735940866</v>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
-        <is>
-          <t>2.21%→2.12%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>884→708</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>지투지바이오</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>1402380053</v>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>0.86%→1.31%</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>130→193</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>에이프릴바이오</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-122</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-941449636</v>
-      </c>
-      <c r="J34" s="16" t="inlineStr">
-        <is>
-          <t>3.08%→1.96%</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>955→833</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>오스코텍</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>339677013</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>4.12%→4.45%</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>715→732</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>-994704038</v>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>9.54%→9.89%</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>539→523</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>303160011</v>
+        <v>938736035</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>6.03%→5.92%</t>
+          <t>3.17%→3.52%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>821→834</t>
+          <t>779→851</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>녹십자</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-10</v>
+        <v>-176</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-685820026</v>
+        <v>-1709822465</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>3.68%→3.71%</t>
+          <t>2.21%→2.18%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>188→178</t>
+          <t>884→708</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>305280012</v>
+        <v>1252125047</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>7.55%→7.29%</t>
+          <t>0.86%→1.22%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>930→942</t>
-        </is>
-      </c>
-      <c r="G37" s="17" t="n"/>
-      <c r="H37" s="17" t="n"/>
-      <c r="I37" s="17" t="n"/>
-      <c r="J37" s="17" t="n"/>
-      <c r="K37" s="17" t="n"/>
+          <t>130→193</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I37" s="15" t="n">
+        <v>-867090633</v>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>3.08%→1.88%</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>955→833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>328865012</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>4.12%→4.50%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>715→732</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-900576034</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>9.54%→9.35%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>539→523</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>297303511</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>6.03%→6.06%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>821→834</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-678930026</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>3.68%→3.84%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>188→178</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>290016011</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>7.55%→7.23%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>930→942</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="B38" s="11" t="n">
+      <c r="B41" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>293408011</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>2.76%→2.77%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="C41" s="11" t="n">
+        <v>266908010</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>2.76%→2.63%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>120→124</t>
         </is>
       </c>
-      <c r="G38" s="17" t="n"/>
-      <c r="H38" s="17" t="n"/>
-      <c r="I38" s="17" t="n"/>
-      <c r="J38" s="17" t="n"/>
-      <c r="K38" s="17" t="n"/>
-    </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="n"/>
-      <c r="C40" s="19" t="n"/>
-      <c r="D40" s="19" t="n"/>
-      <c r="E40" s="19" t="n"/>
-      <c r="F40" s="19" t="n"/>
-      <c r="G40" s="19" t="n"/>
-      <c r="H40" s="19" t="n"/>
-      <c r="I40" s="19" t="n"/>
-      <c r="J40" s="19" t="n"/>
-      <c r="K40" s="19" t="n"/>
-    </row>
-    <row r="42" ht="19" customHeight="1">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="n"/>
-      <c r="C42" s="19" t="n"/>
-      <c r="D42" s="19" t="n"/>
-      <c r="E42" s="19" t="n"/>
-      <c r="F42" s="19" t="n"/>
-      <c r="G42" s="19" t="n"/>
-      <c r="H42" s="19" t="n"/>
-      <c r="I42" s="19" t="n"/>
-      <c r="J42" s="19" t="n"/>
-      <c r="K42" s="19" t="n"/>
-    </row>
-    <row r="44" ht="19" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 7억(2.2%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 9종목</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="17" t="n"/>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억   ·   현금 65억(2.4%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 7종목  /  매도 11종목</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n"/>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="8" t="n"/>
+      <c r="J44" s="8" t="n"/>
+      <c r="K44" s="8" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>1251842378</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>4.87%→5.06%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>299→330</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-195</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-1307682095</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.84%→0.51%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>397→202</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>LS머트리얼즈  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>99555429</v>
+        <v>2801253846</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.31%</t>
+          <t>2.70%→4.05%</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>0→89</t>
+          <t>59→80</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-219</v>
+        <v>-96</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-177512692</v>
+        <v>-1623754091</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.42%</t>
+          <t>1.00%→0.32%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>777→558</t>
+          <t>146→50</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>씨에스베어링</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>13894444</v>
+        <v>757328229</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.72%</t>
+          <t>3.15%→3.59%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>2,565→2,607</t>
+          <t>230→250</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>켐트로닉스  (편출)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-60</v>
+        <v>-66</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-57324017</v>
+        <v>-1221191769</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.48%</t>
+          <t>0.44%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>220→160</t>
+          <t>66→0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>필옵틱스  (신규)</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>96872828</v>
+        <v>890787469</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.31%</t>
+          <t>2.57%→3.04%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>0→34</t>
+          <t>128→144</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-17</v>
+        <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-29882609</v>
+        <v>-799365241</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>4.77%→4.71%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>868→851</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>38569611</v>
+        <v>1229334371</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.20%</t>
+          <t>1.87%→2.80%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>142→158</t>
+          <t>75→90</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-12</v>
+        <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-46756814</v>
+        <v>-974795294</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.10%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>102→90</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>81940024</v>
+        <v>4397667329</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.24%</t>
+          <t>4.40%→5.90%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>33→46</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>한국피아이엠  (편출)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-11</v>
+        <v>-33</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-93724428</v>
+        <v>-1199345762</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.28%</t>
+          <t>0.43%→0.00%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>96→85</t>
+          <t>33→0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>49334015</v>
+        <v>2038960616</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.83%</t>
+          <t>3.60%→4.64%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>50→60</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>인텔리안테크  (편출)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-10</v>
+        <v>-30</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-59160017</v>
+        <v>-1360410411</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.93%</t>
+          <t>0.49%→0.00%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>60→50</t>
+          <t>30→0</t>
         </is>
       </c>
     </row>
@@ -2132,23 +2269,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
-        <v>-7</v>
+        <v>-28</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-12138004</v>
+        <v>-646906595</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.62%</t>
+          <t>0.48%→0.22%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>487→480</t>
+          <t>53→25</t>
         </is>
       </c>
     </row>
@@ -2160,23 +2297,23 @@
       <c r="E54" s="17" t="n"/>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-5</v>
+        <v>-26</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-71230021</v>
+        <v>-1337372804</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.30%→3.09%</t>
+          <t>0.88%→0.49%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>74→69</t>
+          <t>51→25</t>
         </is>
       </c>
     </row>
@@ -2188,85 +2325,791 @@
       <c r="E55" s="17" t="n"/>
       <c r="G55" s="14" t="inlineStr">
         <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-2605301787</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>2.94%→1.74%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>47→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>쎄트렉아이</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-415736126</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.56%→0.32%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>30→20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억   ·   현금 22억(1.1%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 1종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+      <c r="E59" s="6" t="n"/>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="8" t="n"/>
+      <c r="J59" s="8" t="n"/>
+      <c r="K59" s="8" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>5758366788</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>11.42%→15.45%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>367→451</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-231</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-3291749307</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>6.28%→4.42%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>852→621</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-1935339593</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>12.12%→10.90%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>270→248</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-84302982</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>3.37%→3.17%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>686→677</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>인벤티지랩</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-46644990</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>2.75%→2.56%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>555→550</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-69311985</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>3.47%→3.27%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>382→378</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 7억(2.2%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="8" t="n"/>
+      <c r="J68" s="8" t="n"/>
+      <c r="K68" s="8" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈  (신규)</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>99555429</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.31%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>0→89</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-219</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-177512692</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>1.97%→1.42%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>777→558</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>씨에스베어링</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>13894444</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>2.65%→2.72%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>2,565→2,607</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-57324017</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>0.66%→0.48%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>220→160</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>필옵틱스  (신규)</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>96872828</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.31%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>0→34</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-17</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-29882609</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>4.77%→4.71%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>868→851</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>38569611</v>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>1.07%→1.20%</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>142→158</t>
+        </is>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-46756814</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>1.24%→1.10%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>102→90</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>81940024</v>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>0.97%→1.24%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>19→24</t>
+        </is>
+      </c>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-93724428</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>2.56%→2.28%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>96→85</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>49334015</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>2.65%→2.83%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>86→91</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-59160017</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>1.11%→0.93%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>60→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="n"/>
+      <c r="B76" s="17" t="n"/>
+      <c r="C76" s="17" t="n"/>
+      <c r="D76" s="17" t="n"/>
+      <c r="E76" s="17" t="n"/>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-12138004</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>2.64%→2.62%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>487→480</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="n"/>
+      <c r="B77" s="17" t="n"/>
+      <c r="C77" s="17" t="n"/>
+      <c r="D77" s="17" t="n"/>
+      <c r="E77" s="17" t="n"/>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>-71230021</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>3.30%→3.09%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>74→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="n"/>
+      <c r="B78" s="17" t="n"/>
+      <c r="C78" s="17" t="n"/>
+      <c r="D78" s="17" t="n"/>
+      <c r="E78" s="17" t="n"/>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
           <t>테스</t>
         </is>
       </c>
-      <c r="H55" s="15" t="n">
+      <c r="H78" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I55" s="15" t="n">
+      <c r="I78" s="15" t="n">
         <v>-33496810</v>
       </c>
-      <c r="J55" s="16" t="inlineStr">
+      <c r="J78" s="16" t="inlineStr">
         <is>
           <t>2.52%→2.43%</t>
         </is>
       </c>
-      <c r="K55" s="13" t="inlineStr">
+      <c r="K78" s="13" t="inlineStr">
         <is>
           <t>72→69</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="18" t="inlineStr">
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="19" t="n"/>
-      <c r="I57" s="19" t="n"/>
-      <c r="J57" s="19" t="n"/>
-      <c r="K57" s="19" t="n"/>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,157억      오늘 2026-10-13  vs  5일전 2026-10-02      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="19" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="19" t="n"/>
+      <c r="G80" s="19" t="n"/>
+      <c r="H80" s="19" t="n"/>
+      <c r="I80" s="19" t="n"/>
+      <c r="J80" s="19" t="n"/>
+      <c r="K80" s="19" t="n"/>
+    </row>
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B82" s="19" t="n"/>
+      <c r="C82" s="19" t="n"/>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="19" t="n"/>
+      <c r="G82" s="19" t="n"/>
+      <c r="H82" s="19" t="n"/>
+      <c r="I82" s="19" t="n"/>
+      <c r="J82" s="19" t="n"/>
+      <c r="K82" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="19">
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="G45:K45"/>
-    <mergeCell ref="A60:K60"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="G31:K31"/>
-    <mergeCell ref="A44:K44"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
       <b val="1"/>
       <color rgb="007F7F7F"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="8">
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -171,6 +175,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-02 ~ 2026-10-13  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-10-02 ~ 2026-10-13  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,364억   ·   현금 15억(0.3%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 10종목  /  매도 26종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,163억   ·   현금 8억(0.1%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 10종목  /  매도 26종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +670,7 @@
         <v>301</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4533841397</v>
+        <v>4584734335</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +691,7 @@
         <v>-219</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2326480183</v>
+        <v>-2352595215</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +714,7 @@
         <v>173</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13241070487</v>
+        <v>13389703164</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +735,7 @@
         <v>-112</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2337887380</v>
+        <v>-2364130459</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +758,7 @@
         <v>67</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3637563035</v>
+        <v>3678395136</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +779,7 @@
         <v>-47</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1595978577</v>
+        <v>-1613893636</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +802,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>515871863</v>
+        <v>521662590</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +823,7 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1383955633</v>
+        <v>-1399490708</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +846,7 @@
         <v>27</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>965789744</v>
+        <v>976630855</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
         <v>-37</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-3227139144</v>
+        <v>-3263364185</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +890,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1675211556</v>
+        <v>1694016015</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +911,7 @@
         <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-939329751</v>
+        <v>-949873845</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>958439746</v>
+        <v>969198352</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +955,7 @@
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1793399524</v>
+        <v>-1813530659</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +978,7 @@
         <v>13</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>517880863</v>
+        <v>523694140</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +999,7 @@
         <v>-28</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-324615114</v>
+        <v>-328258959</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>486863871</v>
+        <v>492328979</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1043,7 @@
         <v>-23</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-544340856</v>
+        <v>-550451150</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1766939531</v>
+        <v>1786773649</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1087,7 @@
         <v>-22</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-634941832</v>
+        <v>-642069133</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1115,7 @@
         <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1422077623</v>
+        <v>-1438040622</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1131,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-818348783</v>
+        <v>-727741114</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.28%</t>
+          <t>0.58%→0.39%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>171→152</t>
+          <t>71→52</t>
         </is>
       </c>
     </row>
@@ -1159,23 +1164,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-719662809</v>
+        <v>-827534851</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.39%</t>
+          <t>1.72%→1.28%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>71→52</t>
+          <t>171→152</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1199,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-85612777</v>
+        <v>-86573791</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1222,7 +1227,7 @@
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-256367932</v>
+        <v>-259245694</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1250,7 +1255,7 @@
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-871023769</v>
+        <v>-880801120</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1278,7 +1283,7 @@
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-551935854</v>
+        <v>-558131403</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1306,7 +1311,7 @@
         <v>-10</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-858479772</v>
+        <v>-868116315</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1327,23 +1332,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1588089579</v>
+        <v>-469635071</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.85%→1.38%</t>
+          <t>0.38%→0.33%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1355,23 +1360,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-464421877</v>
+        <v>-1605916083</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.33%</t>
+          <t>1.85%→1.38%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1388,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1184819686</v>
+        <v>-500058782</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>6.77%→7.13%</t>
+          <t>0.48%→0.40%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1411,23 +1416,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-494507869</v>
+        <v>-1198119435</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.40%</t>
+          <t>6.77%→7.13%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1451,7 @@
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-129065966</v>
+        <v>-130514747</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1474,7 +1479,7 @@
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-873179768</v>
+        <v>-882981321</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1495,23 +1500,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-905519760</v>
+        <v>-481031575</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.66%</t>
+          <t>6.18%→5.60%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1523,30 +1528,30 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-475691874</v>
+        <v>-915684333</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>6.18%→5.60%</t>
+          <t>2.69%→2.66%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,314억   ·   현금 52억(1.6%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,174억   ·   현금 26억(0.8%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1642,7 +1647,7 @@
         <v>72</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>938736035</v>
+        <v>938735717</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1663,7 +1668,7 @@
         <v>-176</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-1709822465</v>
+        <v>-1709821884</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1686,7 +1691,7 @@
         <v>63</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>1252125047</v>
+        <v>1252124622</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1707,7 +1712,7 @@
         <v>-122</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-867090633</v>
+        <v>-867090338</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1730,7 +1735,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>328865012</v>
+        <v>328864901</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1751,7 +1756,7 @@
         <v>-16</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-900576034</v>
+        <v>-900575728</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1774,7 +1779,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>297303511</v>
+        <v>297303410</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1795,7 +1800,7 @@
         <v>-10</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-678930026</v>
+        <v>-678929795</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1818,7 +1823,7 @@
         <v>12</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>290016011</v>
+        <v>290015912</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1846,7 +1851,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>266908010</v>
+        <v>266907919</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1867,7 +1872,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,827억   ·   현금 65억(2.4%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 7종목  /  매도 11종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,664억   ·   현금 33억(1.2%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 7종목  /  매도 11종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -1963,7 +1968,7 @@
         <v>31</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>1251842378</v>
+        <v>1249950395</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1989,7 @@
         <v>-195</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-1307682095</v>
+        <v>-1305705718</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2007,7 +2012,7 @@
         <v>21</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2801253846</v>
+        <v>2797020146</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2028,7 +2033,7 @@
         <v>-96</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-1623754091</v>
+        <v>-1621300015</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2051,7 +2056,7 @@
         <v>20</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>757328229</v>
+        <v>756183634</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2072,7 +2077,7 @@
         <v>-66</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1221191769</v>
+        <v>-1219346110</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2095,7 +2100,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>890787469</v>
+        <v>889441169</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2109,23 +2114,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-799365241</v>
+        <v>-973322029</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.18%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2144,7 @@
         <v>15</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>1229334371</v>
+        <v>1227476406</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2153,23 +2158,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-974795294</v>
+        <v>-798157114</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2188,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>4397667329</v>
+        <v>4391020874</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2204,7 +2209,7 @@
         <v>-33</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-1199345762</v>
+        <v>-1197533120</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2227,7 +2232,7 @@
         <v>10</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>2038960616</v>
+        <v>2035879014</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2248,7 +2253,7 @@
         <v>-30</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-1360410411</v>
+        <v>-1358354342</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2276,7 +2281,7 @@
         <v>-28</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-646906595</v>
+        <v>-645928887</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -2304,7 +2309,7 @@
         <v>-26</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1337372804</v>
+        <v>-1335351554</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -2332,7 +2337,7 @@
         <v>-17</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-2605301787</v>
+        <v>-2601364241</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2360,7 +2365,7 @@
         <v>-10</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-415736126</v>
+        <v>-415107799</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -2376,7 +2381,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,114억   ·   현금 22억(1.1%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 1종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 11억(0.5%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 1종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -2472,7 +2477,7 @@
         <v>84</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>5758366788</v>
+        <v>5803826072</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2493,7 +2498,7 @@
         <v>-231</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-3291749307</v>
+        <v>-3317735941</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2521,7 +2526,7 @@
         <v>-22</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-1935339593</v>
+        <v>-1950618083</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2549,7 +2554,7 @@
         <v>-9</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-84302982</v>
+        <v>-84968510</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2577,7 +2582,7 @@
         <v>-5</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-46644990</v>
+        <v>-47013228</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2605,7 +2610,7 @@
         <v>-4</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-69311985</v>
+        <v>-69859167</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2621,7 +2626,7 @@
     <row r="67" ht="19" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 321억   ·   현금 7억(2.2%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 9종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 306억   ·   현금 4억(1.1%)      오늘 2026-10-13  vs  5일전 2026-10-02      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B67" s="4" t="n"/>
@@ -2717,7 +2722,7 @@
         <v>89</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>99555429</v>
+        <v>93019240</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
@@ -2738,11 +2743,11 @@
         <v>-219</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-177512692</v>
+        <v>-161429280</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.42%</t>
+          <t>1.88%→1.36%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2761,11 +2766,11 @@
         <v>42</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>13894444</v>
+        <v>13337520</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.72%</t>
+          <t>2.68%→2.74%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -2782,11 +2787,11 @@
         <v>-60</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-57324017</v>
+        <v>-54141600</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.66%→0.48%</t>
+          <t>0.65%→0.48%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -2805,11 +2810,11 @@
         <v>34</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>96872828</v>
+        <v>91439600</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.31%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -2826,11 +2831,11 @@
         <v>-17</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-29882609</v>
+        <v>-27744000</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>4.77%→4.71%</t>
+          <t>4.66%→4.59%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2849,11 +2854,11 @@
         <v>16</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>38569611</v>
+        <v>37971200</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>1.07%→1.20%</t>
+          <t>1.11%→1.24%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2870,11 +2875,11 @@
         <v>-12</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-46756814</v>
+        <v>-47409600</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.10%</t>
+          <t>1.32%→1.18%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -2886,23 +2891,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>81940024</v>
+        <v>47600000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.24%</t>
+          <t>2.69%→2.87%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -2914,11 +2919,11 @@
         <v>-11</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-93724428</v>
+        <v>-92602400</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>2.56%→2.28%</t>
+          <t>2.66%→2.37%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -2930,23 +2935,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>49334015</v>
+        <v>78710000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>2.65%→2.83%</t>
+          <t>0.98%→1.25%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -2958,11 +2963,11 @@
         <v>-10</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-59160017</v>
+        <v>-54944000</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>1.11%→0.93%</t>
+          <t>1.08%→0.91%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -2986,11 +2991,11 @@
         <v>-7</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-12138004</v>
+        <v>-11757200</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>2.64%→2.62%</t>
+          <t>2.69%→2.67%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3014,11 +3019,11 @@
         <v>-5</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-71230021</v>
+        <v>-68510000</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>3.30%→3.09%</t>
+          <t>3.33%→3.13%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3042,11 +3047,11 @@
         <v>-3</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-33496810</v>
+        <v>-33007200</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>2.52%→2.43%</t>
+          <t>2.60%→2.51%</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
@@ -3073,26 +3078,34 @@
       <c r="K80" s="19" t="n"/>
     </row>
     <row r="82" ht="19" customHeight="1">
-      <c r="A82" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B82" s="19" t="n"/>
-      <c r="C82" s="19" t="n"/>
-      <c r="D82" s="19" t="n"/>
-      <c r="E82" s="19" t="n"/>
-      <c r="F82" s="19" t="n"/>
-      <c r="G82" s="19" t="n"/>
-      <c r="H82" s="19" t="n"/>
-      <c r="I82" s="19" t="n"/>
-      <c r="J82" s="19" t="n"/>
-      <c r="K82" s="19" t="n"/>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,107억      오늘 2026-10-13  vs  5일전 2026-10-02      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="n"/>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A58:K58"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:K83"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="G59:K59"/>
     <mergeCell ref="A82:K82"/>

--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-949873845</v>
+        <v>-1813530659</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.66%</t>
+          <t>3.00%→2.43%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>137→107</t>
+          <t>237→207</t>
         </is>
       </c>
     </row>
@@ -948,23 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1813530659</v>
+        <v>-949873845</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>3.00%→2.43%</t>
+          <t>0.90%→0.66%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>237→207</t>
+          <t>137→107</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-727741114</v>
+        <v>-827534851</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.39%</t>
+          <t>1.72%→1.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>71→52</t>
+          <t>171→152</t>
         </is>
       </c>
     </row>
@@ -1164,23 +1164,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-827534851</v>
+        <v>-727741114</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.28%</t>
+          <t>0.58%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>171→152</t>
+          <t>71→52</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-880801120</v>
+        <v>-558131403</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.75%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1276,23 +1276,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-558131403</v>
+        <v>-880801120</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.02%→0.75%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1388,23 +1388,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-500058782</v>
+        <v>-130514747</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.40%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1416,23 +1416,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1198119435</v>
+        <v>-500058782</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>6.77%→7.13%</t>
+          <t>0.48%→0.40%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1444,23 +1444,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-130514747</v>
+        <v>-1198119435</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>6.77%→7.13%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1472,23 +1472,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-882981321</v>
+        <v>-915684333</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.69%</t>
+          <t>2.69%→2.66%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1500,23 +1500,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-481031575</v>
+        <v>-882981321</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>6.18%→5.60%</t>
+          <t>0.87%→0.69%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -1528,23 +1528,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-915684333</v>
+        <v>-481031575</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.66%</t>
+          <t>6.18%→5.60%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-973322029</v>
+        <v>-798157114</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-798157114</v>
+        <v>-973322029</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.18%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1813530659</v>
+        <v>-949873845</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>3.00%→2.43%</t>
+          <t>0.90%→0.66%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>237→207</t>
+          <t>137→107</t>
         </is>
       </c>
     </row>
@@ -948,23 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-949873845</v>
+        <v>-1813530659</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.66%</t>
+          <t>3.00%→2.43%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>137→107</t>
+          <t>237→207</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-827534851</v>
+        <v>-727741114</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.28%</t>
+          <t>0.58%→0.39%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>171→152</t>
+          <t>71→52</t>
         </is>
       </c>
     </row>
@@ -1164,23 +1164,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-727741114</v>
+        <v>-827534851</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.39%</t>
+          <t>1.72%→1.28%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>71→52</t>
+          <t>171→152</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-558131403</v>
+        <v>-880801120</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.02%→0.75%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1276,23 +1276,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-880801120</v>
+        <v>-558131403</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.75%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1332,23 +1332,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-469635071</v>
+        <v>-1605916083</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.33%</t>
+          <t>1.85%→1.38%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>32→25</t>
+          <t>38→31</t>
         </is>
       </c>
     </row>
@@ -1360,23 +1360,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>에이치브이엠</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1605916083</v>
+        <v>-469635071</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.85%→1.38%</t>
+          <t>0.38%→0.33%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>38→31</t>
+          <t>32→25</t>
         </is>
       </c>
     </row>
@@ -1416,23 +1416,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-500058782</v>
+        <v>-1198119435</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.40%</t>
+          <t>6.77%→7.13%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1444,23 +1444,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1198119435</v>
+        <v>-500058782</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>6.77%→7.13%</t>
+          <t>0.48%→0.40%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1472,23 +1472,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-915684333</v>
+        <v>-481031575</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.66%</t>
+          <t>6.18%→5.60%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -1528,23 +1528,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-481031575</v>
+        <v>-915684333</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>6.18%→5.60%</t>
+          <t>2.69%→2.66%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-798157114</v>
+        <v>-973322029</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.18%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-973322029</v>
+        <v>-798157114</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>HPSP</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-949873845</v>
+        <v>-1813530659</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.66%</t>
+          <t>3.00%→2.43%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>137→107</t>
+          <t>237→207</t>
         </is>
       </c>
     </row>
@@ -948,23 +948,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1813530659</v>
+        <v>-949873845</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>3.00%→2.43%</t>
+          <t>0.90%→0.66%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>237→207</t>
+          <t>137→107</t>
         </is>
       </c>
     </row>
@@ -1136,23 +1136,23 @@
       <c r="E17" s="17" t="n"/>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-727741114</v>
+        <v>-827534851</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.58%→0.39%</t>
+          <t>1.72%→1.28%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>71→52</t>
+          <t>171→152</t>
         </is>
       </c>
     </row>
@@ -1164,23 +1164,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-19</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-827534851</v>
+        <v>-727741114</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.28%</t>
+          <t>0.58%→0.39%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>171→152</t>
+          <t>71→52</t>
         </is>
       </c>
     </row>
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-880801120</v>
+        <v>-558131403</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.75%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1276,23 +1276,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-558131403</v>
+        <v>-880801120</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.02%→0.75%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1472,23 +1472,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-481031575</v>
+        <v>-882981321</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>6.18%→5.60%</t>
+          <t>0.87%→0.69%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>183→180</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -1500,23 +1500,23 @@
       <c r="E30" s="17" t="n"/>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-882981321</v>
+        <v>-481031575</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.69%</t>
+          <t>6.18%→5.60%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>183→180</t>
         </is>
       </c>
     </row>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-973322029</v>
+        <v>-798157114</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-798157114</v>
+        <v>-973322029</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.18%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2891,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>47600000</v>
+        <v>78710000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.87%</t>
+          <t>0.98%→1.25%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -2935,23 +2935,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>78710000</v>
+        <v>47600000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.25%</t>
+          <t>2.69%→2.87%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261013.xlsx
+++ b/reports/pdf_rolling5_20261013.xlsx
@@ -1248,23 +1248,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론  (편출)</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-558131403</v>
+        <v>-880801120</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.10%→0.00%</t>
+          <t>1.02%→0.75%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>11→0</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1276,23 +1276,23 @@
       <c r="E22" s="17" t="n"/>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>하나마이크론  (편출)</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-880801120</v>
+        <v>-558131403</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.02%→0.75%</t>
+          <t>0.10%→0.00%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>11→0</t>
         </is>
       </c>
     </row>
@@ -1388,23 +1388,23 @@
       <c r="E26" s="17" t="n"/>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H26" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-130514747</v>
+        <v>-500058782</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.38%</t>
+          <t>0.48%→0.40%</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1416,23 +1416,23 @@
       <c r="E27" s="17" t="n"/>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H27" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1198119435</v>
+        <v>-130514747</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>6.77%→7.13%</t>
+          <t>0.42%→0.38%</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>190→184</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1444,23 +1444,23 @@
       <c r="E28" s="17" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H28" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-500058782</v>
+        <v>-1198119435</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.40%</t>
+          <t>6.77%→7.13%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>190→184</t>
         </is>
       </c>
     </row>
@@ -1472,23 +1472,23 @@
       <c r="E29" s="17" t="n"/>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H29" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-882981321</v>
+        <v>-915684333</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.69%</t>
+          <t>2.69%→2.66%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>15→12</t>
+          <t>48→45</t>
         </is>
       </c>
     </row>
@@ -1528,23 +1528,23 @@
       <c r="E31" s="17" t="n"/>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H31" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-915684333</v>
+        <v>-882981321</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>2.69%→2.66%</t>
+          <t>0.87%→0.69%</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>48→45</t>
+          <t>15→12</t>
         </is>
       </c>
     </row>
@@ -2114,23 +2114,23 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>아이티센글로벌  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-798157114</v>
+        <v>-973322029</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.18%</t>
+          <t>0.35%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>80→30</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2158,23 +2158,23 @@
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>아이티센글로벌  (편출)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-973322029</v>
+        <v>-798157114</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.00%</t>
+          <t>0.56%→0.18%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>80→30</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2891,23 @@
     <row r="74">
       <c r="A74" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B74" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>78710000</v>
+        <v>47600000</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.98%→1.25%</t>
+          <t>2.69%→2.87%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>19→24</t>
+          <t>86→91</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -2935,23 +2935,23 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>47600000</v>
+        <v>78710000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>2.69%→2.87%</t>
+          <t>0.98%→1.25%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>86→91</t>
+          <t>19→24</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
